--- a/extenbooks/AS002_extenbook.xlsx
+++ b/extenbooks/AS002_extenbook.xlsx
@@ -13044,7 +13044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -13083,483 +13083,480 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Status:** ingested  **Year range (book):** 1947-2011</t>
+          <t>***Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wage Equivalent and Corp/Noncorp Split</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Wage Equivalent and Corp/Noncorp Split</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>## Why It Matters</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>## Why It Matters</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WEQ2 = (sigma*PropInc - ECprop)/(1+sigma). Source: Appendix Table 6.8.I.2. Used by AS003 / S603. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>WEQ2 = (sigma*PropInc - ECprop)/(1+sigma). Source: Appendix Table 6.8.I.2. Used by AS003 / S603. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>## Sources (per subseries)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>## Sources (per subseries)</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+          <t>|-----------|---------------|----------|---------------|-------|</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>|-----------|---------------|----------|---------------|-------|</t>
+          <t>| AS002-A | I2 | `PropInc` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| AS002-A | I2 | `PropInc` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| AS002-B | I2 | `ECprop` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| AS002-B | I2 | `ECprop` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| AS002-C | I2 | `WEQ2` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| AS002-C | I2 | `WEQ2` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| AS002-D | I2 | `WEQ1` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| AS002-D | I2 | `WEQ1` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| AS002-E | I2 | `Pnoncorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| AS002-E | I2 | `Pnoncorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| AS002-F | I2 | `Pcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>| AS002-F | I2 | `Pcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| AS002-G | I2 | `s` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>| AS002-G | I2 | `s` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Verbatim transcription of Shaikh (2016) Appendix 6.8 columns; extension recipe in EPR re-fetches NIPA / BEA FA / IRS components.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Verbatim transcription of Shaikh (2016) Appendix 6.8 columns; extension recipe in EPR re-fetches NIPA / BEA FA / IRS components.</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>## Year Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>## Year Coverage</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Book period: 1947-2011. Vintage-stable extension recipe in `AS002_EPR.md`.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Book period: 1947-2011. Vintage-stable extension recipe in `AS002_EPR.md`.</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>## Units</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>## Units</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>billions_current_usd</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>billions_current_usd</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>## Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>## Caveats</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>* Vintage-drift exposure: BEA / NIPA comprehensive revisions in 2013 and 2018 alter historical values; document vintage_year at fetch time.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>* Vintage-drift exposure: BEA / NIPA comprehensive revisions in 2013 and 2018 alter historical values; document vintage_year at fetch time.</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>## Validation Expectation</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>## Validation Expectation</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>`V03_AS002_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4">
+    <row r="55">
+      <c r="A55" s="4">
         <f>== EPR: AS002_EPR.md ===</f>
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t># AS002 — Wage Equivalent and Corp/Noncorp Split (Extension Provenance Record)</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t># AS002 — Wage Equivalent and Corp/Noncorp Split (Extension Provenance Record)</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>## Method</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published AS002 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published AS002 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>3. Re-run the construction formula end-to-end.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>## Worked Example</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>## Worked Example</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>For AS002, the Phase 5 round-trip validation reads `AS002_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>For AS002, the Phase 5 round-trip validation reads `AS002_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>## No-Proxy Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>## No-Proxy Disclosure</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>## No-Synthetic Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>## No-Synthetic Disclosure</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>## Failure Mode Table</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Response |</t>
+          <t>|---------|-----------|----------|</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>|---------|-----------|----------|</t>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>## Anti-Degradation Compliance</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
         </is>
@@ -14123,11 +14120,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14150,76 +14147,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Wage Equivalent and Corp/Noncorp Split</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/AS002_research.json", "adequacy_report": "Technical/docs/chapters/CH6_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/AS002_DPR.md", "epr": "Technical/docs/series/AS002_EPR.md", "loader": "Technical/code/L01_loaders/L01_AS002_load.py", "processor": "Technical/code/P02_processors/P02_AS002_construct.py", "validator": "Technical/code/V03_validators/V03_AS002_validate.py", "processed": "Technical/data/processed/AS002.parquet", "chopped_csv": "Technical/chopped/AS002.csv", "extenbook_xlsx": "Technical/extenbooks/AS002_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:43:17.420354+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
